--- a/Config/AssetsPath.xlsx
+++ b/Config/AssetsPath.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C273B6C-DEAA-44BE-A34E-5F76A04FF636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98CD940-C487-4DDE-AD0C-0F129BABF624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-2910" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="90" windowWidth="21850" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
   <si>
     <t>#</t>
   </si>
@@ -208,9 +208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/GameMain/Prefeb/Charactor/enemy0/Z_Attack.anim</t>
-  </si>
-  <si>
     <t>僵尸倒地</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -240,9 +237,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/GameMain/Prefeb/Sfx/CFXR3 Hit Fire B (Air).prefab</t>
-  </si>
-  <si>
     <t>Assets/GameMain/Image/Icons/ItemIcon/DarkMountain.png</t>
   </si>
   <si>
@@ -257,9 +251,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/GameMain/Prefeb/Charactor/HorizontalSwing.anim</t>
-  </si>
-  <si>
     <t>Assets/GameMain/Prefeb/Charactor/qizi0/KyleRobot.prefab</t>
   </si>
   <si>
@@ -361,9 +352,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/GameMain/Prefeb/Charactor/shield_power.anim</t>
-  </si>
-  <si>
     <t>护盾特效</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -408,6 +396,53 @@
   </si>
   <si>
     <t>Assets/GameMain/Audio/cutting_with_a_katana.wav</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Skill/Z_Attack.anim</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Skill/HorizontalSwing.anim</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Skill/shield_power.anim</t>
+  </si>
+  <si>
+    <t>施法开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Skill/SpellCast_Start.anim</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Skill/SpellCast_End.anim</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Skill/CastingLoop.anim</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Prefeb/Sfx/hitSfx/CFXR3 Hit Fire B (Air).prefab</t>
+  </si>
+  <si>
+    <t>蓝色爆炸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Prefeb/Sfx/Boom/BoomBlue.prefab</t>
+  </si>
+  <si>
+    <t>爆炸音效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Audio/short_bomb.mp3</t>
   </si>
 </sst>
 </file>
@@ -743,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -865,10 +900,10 @@
         <v>2001</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -876,10 +911,10 @@
         <v>2002</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -887,10 +922,10 @@
         <v>2003</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -901,7 +936,7 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -909,10 +944,10 @@
         <v>2005</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -928,7 +963,7 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -944,7 +979,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -952,10 +987,10 @@
         <v>3301</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -963,10 +998,10 @@
         <v>3302</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -974,287 +1009,287 @@
         <v>3303</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>85</v>
+      <c r="B24">
+        <v>3304</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B25">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26">
         <v>3501</v>
       </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B27">
-        <v>4000</v>
-      </c>
-      <c r="C27" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B28">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>4004</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>24</v>
+        <v>4003</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>4501</v>
+        <v>4005</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>4503</v>
+        <v>4502</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>4800</v>
+        <v>4503</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>4801</v>
+        <v>4800</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>4802</v>
+        <v>4801</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>4803</v>
+        <v>4802</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>4804</v>
+        <v>4803</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>4805</v>
+        <v>4804</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>4806</v>
+        <v>4805</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43">
+        <v>4806</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B44">
         <v>4807</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B45">
-        <v>6001</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" t="s">
-        <v>45</v>
-      </c>
+      <c r="C45" s="1"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B46">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>6011</v>
+        <v>6004</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
         <v>53</v>
@@ -1262,84 +1297,139 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>6101</v>
+        <v>6012</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B52">
+        <v>6101</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B53">
         <v>6102</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>16</v>
+      <c r="C53" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>10001</v>
+        <v>6103</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>10002</v>
+        <v>6104</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D55" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>12001</v>
+        <v>6105</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B57">
-        <v>12002</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" t="s">
-        <v>103</v>
+      <c r="A57" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58">
+        <v>10001</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>10002</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <v>12001</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B61">
+        <v>12002</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B62">
         <v>12003</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" t="s">
-        <v>105</v>
+      <c r="C62" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <v>12004</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Config/AssetsPath.xlsx
+++ b/Config/AssetsPath.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98CD940-C487-4DDE-AD0C-0F129BABF624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5705A67-E466-47A5-86C8-AED70E82BB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="90" windowWidth="21850" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="29890" windowHeight="16270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
   <si>
     <t>#</t>
   </si>
@@ -443,6 +443,20 @@
   </si>
   <si>
     <t>Assets/GameMain/Audio/short_bomb.mp3</t>
+  </si>
+  <si>
+    <t>胜利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Defeat.anim</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Animation/Victory.anim</t>
   </si>
 </sst>
 </file>
@@ -778,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -1308,127 +1322,149 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>6101</v>
+        <v>6013</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>6102</v>
+        <v>6014</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>6103</v>
+        <v>6101</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>6105</v>
+        <v>6103</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>16</v>
+      <c r="B57">
+        <v>6104</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>10001</v>
+        <v>6105</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B59">
-        <v>10002</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D59" t="s">
-        <v>91</v>
+      <c r="A59" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60">
-        <v>12001</v>
+        <v>10001</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>12002</v>
+        <v>10002</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>12003</v>
+        <v>12001</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B63">
+        <v>12002</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B64">
+        <v>12003</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D64" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B65">
         <v>12004</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D65" t="s">
         <v>115</v>
       </c>
     </row>

--- a/Config/AssetsPath.xlsx
+++ b/Config/AssetsPath.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5705A67-E466-47A5-86C8-AED70E82BB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F73D23-8CEB-4513-9149-DB0D544077BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="29890" windowHeight="16270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
   <si>
     <t>#</t>
   </si>
@@ -457,6 +457,13 @@
   </si>
   <si>
     <t>Assets/GameMain/Animation/Victory.anim</t>
+  </si>
+  <si>
+    <t>村民</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Prefeb/Charactor/LowpolyCharacterVillager/HumanMale.prefab</t>
   </si>
 </sst>
 </file>
@@ -792,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -992,202 +999,202 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20">
+        <v>3052</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B21">
-        <v>3301</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B24">
+        <v>3303</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B25">
         <v>3304</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>112</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B26">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B27">
         <v>3501</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>83</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B28">
-        <v>4000</v>
-      </c>
-      <c r="C28" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B29">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>4004</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>24</v>
+        <v>4003</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>4501</v>
+        <v>4005</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>4503</v>
+        <v>4502</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>4800</v>
+        <v>4503</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>4801</v>
+        <v>4800</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>4802</v>
+        <v>4801</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
         <v>74</v>
@@ -1195,276 +1202,287 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>4803</v>
+        <v>4802</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>4804</v>
+        <v>4803</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>4805</v>
+        <v>4804</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>4806</v>
+        <v>4805</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B44">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D44" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="B45">
+        <v>4807</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B46">
-        <v>6001</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" t="s">
-        <v>45</v>
-      </c>
+      <c r="C46" s="1"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B48">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>6011</v>
+        <v>6004</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B52">
-        <v>6013</v>
+        <v>6012</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>6014</v>
+        <v>6013</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>6101</v>
+        <v>6014</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58">
+        <v>6104</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D58" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B59">
         <v>6105</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B60">
-        <v>10001</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D61" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>12001</v>
+        <v>10002</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>12002</v>
+        <v>12001</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B64">
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D64" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65">
+        <v>12003</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B66">
         <v>12004</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D66" t="s">
         <v>115</v>
       </c>
     </row>

--- a/Config/AssetsPath.xlsx
+++ b/Config/AssetsPath.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F73D23-8CEB-4513-9149-DB0D544077BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3A14F6-BE3D-436B-B082-C48CBCEA0439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="29890" windowHeight="16270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="144">
   <si>
     <t>#</t>
   </si>
@@ -464,6 +464,82 @@
   </si>
   <si>
     <t>Assets/GameMain/Prefeb/Charactor/LowpolyCharacterVillager/HumanMale.prefab</t>
+  </si>
+  <si>
+    <t>技能护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Image/Icons/ItemIcon/UI_Skill_Icon_Buff.png</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Image/Icons/ItemIcon/UI_Skill_Icon_SpiritArrows.png</t>
+  </si>
+  <si>
+    <t>施法飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Image/Icons/ItemIcon/UI_Skill_Icon_Arrow_Barrage.png</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Image/Icons/ItemIcon/UI_Skill_Icon_Slash.png</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Image/Icons/ItemIcon/UI_Skill_Icon_Reflect.png</t>
+  </si>
+  <si>
+    <t>狂热</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋转斧头子弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Prefeb/Weapons/axe_bullet.prefab</t>
+  </si>
+  <si>
+    <t>电击声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Audio/electronic_02.wav</t>
+  </si>
+  <si>
+    <t>切割声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Audio/SWORD_27.wav</t>
+  </si>
+  <si>
+    <t>提示界面出场音效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Audio/SFX_UI_Click_Designed_Liquid_Negative_Close_1.wav</t>
+  </si>
+  <si>
+    <t>子弹命中声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Audio/Bullet Impact 14.wav</t>
+  </si>
+  <si>
+    <t>Assets/GameMain/Audio/Action 3 (Loop).wav</t>
+  </si>
+  <si>
+    <t>战斗音乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗胜利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/GameMain/Audio/Victory.wav</t>
   </si>
 </sst>
 </file>
@@ -799,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -972,518 +1048,650 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B17">
+        <v>2006</v>
+      </c>
+      <c r="C17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B18">
-        <v>3001</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B19">
-        <v>3051</v>
+        <v>3001</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B20">
+        <v>3051</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B21">
         <v>3052</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>120</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <v>3301</v>
-      </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25">
+        <v>3303</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B26">
         <v>3304</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>112</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B27">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B28">
         <v>3501</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>83</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B29">
-        <v>4000</v>
-      </c>
-      <c r="C29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B32">
+        <v>4002</v>
+      </c>
+      <c r="C32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33">
         <v>4003</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>23</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B33">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34">
         <v>4004</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B34">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35">
         <v>4005</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B35">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36">
         <v>4501</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B36">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B37">
         <v>4502</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B37">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B38">
         <v>4503</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B38">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>4504</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>4505</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>4506</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>4507</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>4508</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B44">
         <v>4800</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D44" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B39">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B45">
         <v>4801</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B40">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B46">
         <v>4802</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D46" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B41">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B47">
         <v>4803</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D47" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B42">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B48">
         <v>4804</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D48" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B43">
-        <v>4805</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B44">
-        <v>4806</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B45">
-        <v>4807</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B47">
-        <v>6001</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B48">
-        <v>6002</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>6003</v>
+        <v>4805</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B50">
-        <v>6004</v>
+        <v>4806</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>6011</v>
+        <v>4807</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D51" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B52">
-        <v>6012</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" t="s">
-        <v>52</v>
-      </c>
+      <c r="A52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="1"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>6013</v>
+        <v>6001</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54">
-        <v>6014</v>
+        <v>6002</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B55">
-        <v>6101</v>
+        <v>6003</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B56">
-        <v>6102</v>
+        <v>6004</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B57">
-        <v>6103</v>
+        <v>6011</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58">
-        <v>6104</v>
+        <v>6012</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59">
-        <v>6105</v>
+        <v>6013</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>16</v>
+      <c r="B60">
+        <v>6014</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61">
-        <v>10001</v>
+        <v>6101</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62">
-        <v>10002</v>
+        <v>6102</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>12001</v>
+        <v>6103</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B64">
+        <v>6104</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B65">
+        <v>6105</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B67">
+        <v>10001</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B68">
+        <v>10002</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D68" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <v>10003</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B70">
+        <v>10004</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D70" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B71">
+        <v>10005</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D71" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <v>12001</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B73">
         <v>12002</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D73" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B65">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B74">
         <v>12003</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D74" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B66">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B75">
         <v>12004</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D75" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B76">
+        <v>12005</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B77">
+        <v>12006</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D77" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <v>12007</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D78" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
